--- a/data/Lop2/ToanTiengAnh/ToanTiengAnh_Lop2.xlsx
+++ b/data/Lop2/ToanTiengAnh/ToanTiengAnh_Lop2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4.WEB\daubifamily.github.io-main\data\Lop2\ToanTiengAnh\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\9.WebGithub\daubifamily.github.io\data\Lop2\ToanTiengAnh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA684FEB-11F7-4168-9D54-428D61699C19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C886DE-DE38-428A-BD49-3C0E3CC8BB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="10690" windowWidth="19420" windowHeight="10420" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
